--- a/AAII_Financials/Yearly/NPSCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NPSCY_YR_FIN.xlsx
@@ -656,160 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>63288700</v>
+      </c>
+      <c r="E8" s="3">
         <v>58067700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>58630100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>59996600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>56070700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>43664700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>55031700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>55752600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>53791900</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>54202100</v>
+      </c>
+      <c r="E9" s="3">
         <v>48908000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49461700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>50265800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>46011300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>38553200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>49370500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>48655300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>46597500</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9086600</v>
+      </c>
+      <c r="E10" s="3">
         <v>9159700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9168400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9730800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10059400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5111500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5661200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7097300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7194400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,41 +836,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>447900</v>
+      </c>
+      <c r="E12" s="3">
         <v>435100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>401100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>443000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>449200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>476300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>586900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>650100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>697400</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,75 +905,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1783000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1141100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>614700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>149100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>809600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1195500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4526100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>830200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>457700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>335100</v>
+      </c>
+      <c r="E15" s="3">
         <v>242000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>204000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>172900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>162800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>154500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>91900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3526300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3277800</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +993,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>60669400</v>
+      </c>
+      <c r="E17" s="3">
         <v>54161800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>54157700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>54275500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>50275900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>42838100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>54628500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>53547100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>51364500</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2619300</v>
+      </c>
+      <c r="E18" s="3">
         <v>3905900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4472400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5721100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5794800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>826600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>403300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2205500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2427400</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,173 +1081,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-618300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-852900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1252400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1045600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1902800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-443800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-317400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-806100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-568400</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3572600</v>
+      </c>
+      <c r="E21" s="3">
         <v>5000800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5928800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6939600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7860300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1424900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>812600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6537900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6273600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>563500</v>
+      </c>
+      <c r="E22" s="3">
         <v>255100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>201700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>157400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>179300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>201600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>202700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>172700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>200900</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1086800</v>
+      </c>
+      <c r="E23" s="3">
         <v>3501700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5050900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6520900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6724500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-78300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3936500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2245000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2558800</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>805400</v>
+      </c>
+      <c r="E24" s="3">
         <v>944300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1164100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>963800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1227400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>96500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>23700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-79500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>560700</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1294,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>281500</v>
+      </c>
+      <c r="E26" s="3">
         <v>2557400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3886800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5557100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5497100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-174700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3960100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2324500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1998100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E27" s="3">
         <v>2338800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3632100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5220800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5248300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-293200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4010300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2266700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1702700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1438,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1510,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>618300</v>
+      </c>
+      <c r="E32" s="3">
         <v>852900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1252400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1045600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1902800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>443800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>317400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>806100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>568400</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E33" s="3">
         <v>2338800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3632100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5220800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5248300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-293200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4010300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2266700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1702700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1618,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E35" s="3">
         <v>2338800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3632100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5220800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5248300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-293200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4010300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2266700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1702700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,41 +1730,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2900900</v>
+      </c>
+      <c r="E41" s="3">
         <v>4491100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2967800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5043200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4537800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3250200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2690100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1472600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1345200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1701,248 +1791,272 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>115900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>116300</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11120600</v>
+      </c>
+      <c r="E43" s="3">
         <v>9552300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10498700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7991800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7735900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7281300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7682000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8738700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7834300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17458600</v>
+      </c>
+      <c r="E44" s="3">
         <v>14685300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>15051800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>15691800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14465400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12200400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14239300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14142400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13180400</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1786500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1645700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1632000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1893800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2203800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1433600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1270800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1333300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1373700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33266700</v>
+      </c>
+      <c r="E46" s="3">
         <v>30374400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>30150300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>30620600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28942900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24165600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25882200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25802800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23849900</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13817900</v>
+      </c>
+      <c r="E47" s="3">
         <v>14601100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15531700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>14068300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14465600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14127300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13244800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7157700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7525400</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37980300</v>
+      </c>
+      <c r="E48" s="3">
         <v>24958700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23014400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24580400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25781900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27518300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>27008800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29299400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29413500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6871100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2236200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1640000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1673800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1583100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1285400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1321200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1434300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1312500</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,9 +2123,12 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2031,17 +2151,20 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>8151000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10599500</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2195,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>92202000</v>
+      </c>
+      <c r="E54" s="3">
         <v>73072500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>70838200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71968800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>72074900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>68481100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69189800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>72642600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>73029800</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,206 +2266,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14717200</v>
+      </c>
+      <c r="E57" s="3">
         <v>11161100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12500200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11976900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12572400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12502500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13473700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7409200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7368800</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3182300</v>
+      </c>
+      <c r="E58" s="3">
         <v>3161700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3580000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3031800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2833300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2793700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3502700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4650800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4758600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>796000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1273300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>989500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>742000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1217600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>719600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>636500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7798700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8212400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18695600</v>
+      </c>
+      <c r="E60" s="3">
         <v>15596200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17069700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15750700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16623300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16015800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17613000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19858700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20339900</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>29359100</v>
+      </c>
+      <c r="E61" s="3">
         <v>13583000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14347600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17274200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19017200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20346000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19626400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16730200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15558300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3142900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2811300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2313200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2312700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2464000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1755400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1642900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1558900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1409600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2587,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54312900</v>
+      </c>
+      <c r="E66" s="3">
         <v>33650400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35428600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37016000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39983300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>40168200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41340600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40088100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39840300</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2783,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23597700</v>
+      </c>
+      <c r="E72" s="3">
         <v>25509100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>23308900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>23163000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20709000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17272600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17387700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20757800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20165300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2927,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34781600</v>
+      </c>
+      <c r="E76" s="3">
         <v>35949100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>31587200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>31452900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>28548800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24955000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24549900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29156100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29537100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2999,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E81" s="3">
         <v>2338800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3632100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5220800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5248300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-293200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4010300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2266700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1702700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3095,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3609400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2572600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2399900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2558900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2722600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2629900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3878500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3495600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3244700</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3308,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4508900</v>
+      </c>
+      <c r="E89" s="3">
         <v>6534900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6678500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4974500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5069700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3645500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4594100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4082100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4571700</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3363,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5428600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3993000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3083200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3535700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3844900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4157500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4280200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3959600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3878600</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3468,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17843300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3088000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4698400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2757600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3119900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3517500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3212100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3445600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3419500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,41 +3523,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>921200</v>
+      </c>
+      <c r="E96" s="3">
         <v>1082400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1005700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1248400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>607400</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>428400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>638100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>624200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3664,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11863200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2092400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3596200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1486900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-504800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>476400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-135500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-387100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-988400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>142600</v>
+      </c>
+      <c r="E101" s="3">
         <v>138900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>151500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>167900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>132700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>28600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-72800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-66100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>14500</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1328700</v>
+      </c>
+      <c r="E102" s="3">
         <v>1493400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1464500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>897900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1577700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>633000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1173600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>183300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>178300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
